--- a/Test-A.xlsx
+++ b/Test-A.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/91065edc839078b3/Documents/repos/VBA/windowsforms-recon/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{249C9F99-4324-446E-AB88-A9D5E2CD5966}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{249C9F99-4324-446E-AB88-A9D5E2CD5966}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ACE8E8ED-379E-4AEB-B5BC-E10E6582DA5F}"/>
   <bookViews>
-    <workbookView xWindow="-78" yWindow="0" windowWidth="11676" windowHeight="13758" xr2:uid="{3307ADA7-C68A-4477-9580-39F2A8A543A9}"/>
+    <workbookView xWindow="45984" yWindow="0" windowWidth="23232" windowHeight="9864" xr2:uid="{3307ADA7-C68A-4477-9580-39F2A8A543A9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -445,6 +445,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D89CA0B1-D909-4D5B-8871-A979519109EB}">
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
